--- a/data/trans_orig/P36B16-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36B16-Habitat-trans_orig.xlsx
@@ -760,17 +760,17 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4362</t>
+          <t>4727</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1648</t>
+          <t>1733</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11559</t>
+          <t>12750</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,17 +795,17 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>4362</t>
+          <t>4727</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1553</t>
+          <t>1785</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12127</t>
+          <t>13368</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>53239</t>
+          <t>57430</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39277</t>
+          <t>43400</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>73264</t>
+          <t>75994</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>56874</t>
+          <t>64303</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46647</t>
+          <t>52812</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>69639</t>
+          <t>79567</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>110113</t>
+          <t>121733</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>92439</t>
+          <t>102726</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>134260</t>
+          <t>144135</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,14%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>408113</t>
+          <t>438040</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>381032</t>
+          <t>412074</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>435188</t>
+          <t>464675</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>63,42%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>59,66%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>433623</t>
+          <t>459185</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>412552</t>
+          <t>437626</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>453199</t>
+          <t>480802</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>65,75%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>841737</t>
+          <t>897224</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>807244</t>
+          <t>858803</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>873071</t>
+          <t>930575</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>64,28%</t>
+          <t>63,1%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>60,39%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>65,44%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>164463</t>
+          <t>184278</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>141444</t>
+          <t>159710</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>189688</t>
+          <t>210216</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>171098</t>
+          <t>194631</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>154044</t>
+          <t>176341</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>190357</t>
+          <t>215566</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>335561</t>
+          <t>378908</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>306183</t>
+          <t>345548</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>367308</t>
+          <t>409195</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,78%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>9626</t>
+          <t>10963</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4218</t>
+          <t>5029</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21357</t>
+          <t>26044</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>7998</t>
+          <t>8441</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3792</t>
+          <t>3968</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18251</t>
+          <t>18932</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,22 +1247,22 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>17624</t>
+          <t>19404</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>10144</t>
+          <t>10892</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>32552</t>
+          <t>34894</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>673955</t>
+          <t>731287</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>673955</t>
+          <t>731287</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>673955</t>
+          <t>731287</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1309397</t>
+          <t>1421996</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1309397</t>
+          <t>1421996</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1309397</t>
+          <t>1421996</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>10294</t>
+          <t>10794</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4193</t>
+          <t>5213</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21664</t>
+          <t>22118</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,67 +1442,67 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>9140</t>
+          <t>9772</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4800</t>
+          <t>5287</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14609</t>
+          <t>15774</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>20566</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>12850</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>32346</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>1,53%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>19433</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>11149</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>29806</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>48507</t>
+          <t>55409</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23794</t>
+          <t>42836</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>71411</t>
+          <t>74433</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>87929</t>
+          <t>94881</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>72244</t>
+          <t>78021</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>105895</t>
+          <t>115315</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>136436</t>
+          <t>150290</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>90254</t>
+          <t>126604</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>166455</t>
+          <t>176374</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,32%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>576993</t>
+          <t>637766</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>285620</t>
+          <t>599552</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>738830</t>
+          <t>675538</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>60,8%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>57,16%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>64,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>571729</t>
+          <t>628368</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>543813</t>
+          <t>598567</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>596651</t>
+          <t>656755</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>55,94%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>61,38%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1148721</t>
+          <t>1266134</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>762203</t>
+          <t>1218861</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1312730</t>
+          <t>1311849</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>59,75%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>57,52%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>61,91%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>295028</t>
+          <t>322506</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>137613</t>
+          <t>287368</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>385714</t>
+          <t>357891</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>271604</t>
+          <t>316662</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>249102</t>
+          <t>290007</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>296882</t>
+          <t>344887</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>566632</t>
+          <t>639168</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>370973</t>
+          <t>596524</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>652905</t>
+          <t>686254</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>32,39%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>262042</t>
+          <t>22441</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17898</t>
+          <t>14017</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>739719</t>
+          <t>35750</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>62,01%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>16830</t>
+          <t>20307</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10600</t>
+          <t>13703</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26284</t>
+          <t>29145</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>278872</t>
+          <t>42748</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>35256</t>
+          <t>30908</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>878623</t>
+          <t>60335</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>957231</t>
+          <t>1069989</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>957231</t>
+          <t>1069989</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>957231</t>
+          <t>1069989</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2150095</t>
+          <t>2118906</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2150095</t>
+          <t>2118906</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2150095</t>
+          <t>2118906</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3673</t>
+          <t>7779</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>2290</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10226</t>
+          <t>19163</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>7453</t>
+          <t>8730</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2911</t>
+          <t>5012</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13585</t>
+          <t>15233</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>11126</t>
+          <t>16509</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5831</t>
+          <t>9674</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19301</t>
+          <t>27410</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>59413</t>
+          <t>67439</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>44818</t>
+          <t>52559</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>78670</t>
+          <t>87349</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>69514</t>
+          <t>79951</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30614</t>
+          <t>66319</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>96450</t>
+          <t>97871</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>128927</t>
+          <t>147390</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>86066</t>
+          <t>125249</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>162385</t>
+          <t>175134</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,84%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>411406</t>
+          <t>452042</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>379927</t>
+          <t>416617</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>440253</t>
+          <t>481882</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>56,29%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>51,88%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>427523</t>
+          <t>447987</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>223594</t>
+          <t>420475</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>565950</t>
+          <t>474674</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>55,15%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>51,77%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>58,44%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>838930</t>
+          <t>900029</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>575774</t>
+          <t>854367</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>973376</t>
+          <t>937505</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>55,72%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>52,89%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>58,04%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>212796</t>
+          <t>254320</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>189548</t>
+          <t>224068</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>244767</t>
+          <t>282799</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>422258</t>
+          <t>264066</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>264561</t>
+          <t>238830</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>666792</t>
+          <t>289453</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>635054</t>
+          <t>518387</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>477424</t>
+          <t>481925</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>953580</t>
+          <t>563617</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>34,89%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>17391</t>
+          <t>21493</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>9599</t>
+          <t>12050</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>30441</t>
+          <t>36771</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>6618</t>
+          <t>11525</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2367</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11597</t>
+          <t>20572</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>24009</t>
+          <t>33018</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12821</t>
+          <t>22287</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>37225</t>
+          <t>50279</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>14131</t>
+          <t>14521</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8430</t>
+          <t>8558</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22959</t>
+          <t>24316</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>15756</t>
+          <t>19809</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9749</t>
+          <t>12532</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24832</t>
+          <t>29249</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>29887</t>
+          <t>34330</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>21347</t>
+          <t>24779</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>41340</t>
+          <t>46586</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>103571</t>
+          <t>108199</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>86271</t>
+          <t>88976</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>124932</t>
+          <t>127702</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>142182</t>
+          <t>144710</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>110151</t>
+          <t>127195</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>165285</t>
+          <t>165523</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>245753</t>
+          <t>252909</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>211558</t>
+          <t>227185</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>278343</t>
+          <t>283148</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,45%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>512044</t>
+          <t>534884</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>479265</t>
+          <t>500744</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>544952</t>
+          <t>566388</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>55,25%</t>
+          <t>54,03%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>57,21%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>580782</t>
+          <t>624401</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>470362</t>
+          <t>594283</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>630904</t>
+          <t>655047</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>55,96%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>53,26%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1092826</t>
+          <t>1159284</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>974830</t>
+          <t>1114317</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1153748</t>
+          <t>1206215</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>52,92%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>57,28%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>274189</t>
+          <t>305829</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>245530</t>
+          <t>276370</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>306659</t>
+          <t>339761</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>331048</t>
+          <t>297424</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>270581</t>
+          <t>268993</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>485344</t>
+          <t>326143</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>605237</t>
+          <t>603254</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>536329</t>
+          <t>562431</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>785166</t>
+          <t>651168</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>30,92%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>22896</t>
+          <t>26628</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>15222</t>
+          <t>18037</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>36088</t>
+          <t>41040</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>21980</t>
+          <t>29440</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>14361</t>
+          <t>20687</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>33324</t>
+          <t>41031</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>44876</t>
+          <t>56068</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>32497</t>
+          <t>43610</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>60693</t>
+          <t>75793</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1091747</t>
+          <t>1115783</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1091747</t>
+          <t>1115783</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1091747</t>
+          <t>1115783</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2018578</t>
+          <t>2105845</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2018578</t>
+          <t>2105845</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2018578</t>
+          <t>2105845</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,32 +3453,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>28097</t>
+          <t>33094</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>17911</t>
+          <t>22691</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>41885</t>
+          <t>49151</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>36710</t>
+          <t>43037</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>26285</t>
+          <t>32958</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>50782</t>
+          <t>57572</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>64807</t>
+          <t>76132</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>49422</t>
+          <t>59512</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>82907</t>
+          <t>95583</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>264731</t>
+          <t>288477</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>209287</t>
+          <t>253624</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>305810</t>
+          <t>328688</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>356498</t>
+          <t>383844</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>288961</t>
+          <t>353292</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>400882</t>
+          <t>416772</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>621230</t>
+          <t>672321</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>537359</t>
+          <t>626851</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>688465</t>
+          <t>725902</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1908556</t>
+          <t>2062732</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1478008</t>
+          <t>1999908</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2075082</t>
+          <t>2130598</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>58,39%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>56,61%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,67 +3714,67 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2013657</t>
+          <t>2159939</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1622787</t>
+          <t>2106401</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2165061</t>
+          <t>2217038</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>57,92%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
+          <t>59,45%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>5186</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>4222671</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>4129249</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>4300041</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>58,15%</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>56,86%</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
           <t>59,21%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>5186</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>3922213</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>3370567</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>4191834</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>55,12%</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>47,37%</t>
-        </is>
-      </c>
-      <c r="W30" s="2" t="inlineStr">
-        <is>
-          <t>58,91%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>946477</t>
+          <t>1066933</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>742508</t>
+          <t>1008272</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1039801</t>
+          <t>1128449</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>1196008</t>
+          <t>1072784</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1009956</t>
+          <t>1024179</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1653539</t>
+          <t>1121302</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>2142484</t>
+          <t>2139717</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1905098</t>
+          <t>2061876</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>2638603</t>
+          <t>2223976</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>30,62%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>311956</t>
+          <t>81526</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>66134</t>
+          <t>63313</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1005545</t>
+          <t>108949</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>53426</t>
+          <t>69713</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>39924</t>
+          <t>56148</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>69532</t>
+          <t>88744</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>365382</t>
+          <t>151238</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>116360</t>
+          <t>125158</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1245530</t>
+          <t>179587</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3656299</t>
+          <t>3729317</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3656299</t>
+          <t>3729317</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3656299</t>
+          <t>3729317</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>7116116</t>
+          <t>7262079</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>7116116</t>
+          <t>7262079</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>7116116</t>
+          <t>7262079</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
